--- a/app/src/androidTest/assets/行测基础示例.xlsx
+++ b/app/src/androidTest/assets/行测基础示例.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="题库" sheetId="1" r:id="rId1"/>
+    <sheet name="试卷" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t xml:space="preserve">题型</t>
   </si>
@@ -17,6 +17,9 @@
   </si>
   <si>
     <t xml:space="preserve">材料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图片</t>
   </si>
   <si>
     <t xml:space="preserve">选项A</t>
@@ -412,18 +415,19 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2"/>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D2"/>
       <c r="E2" t="s">
         <v>20</v>
       </c>
@@ -458,20 +462,21 @@
         <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3"/>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
+      <c r="D3"/>
       <c r="E3" t="s">
         <v>34</v>
       </c>
@@ -494,7 +499,7 @@
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -506,36 +511,37 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4"/>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
+      <c r="D4"/>
       <c r="E4" t="s">
         <v>44</v>
       </c>
-      <c r="F4"/>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
       <c r="G4"/>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H4"/>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
         <v>46</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
         <v>27</v>
@@ -550,20 +556,21 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5"/>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
+      <c r="D5"/>
       <c r="E5" t="s">
         <v>50</v>
       </c>
@@ -583,10 +590,10 @@
         <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
         <v>28</v>
@@ -598,20 +605,21 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6"/>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
+      <c r="D6"/>
       <c r="E6" t="s">
         <v>58</v>
       </c>
@@ -631,37 +639,38 @@
         <v>63</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
         <v>28</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O6" t="s">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>66</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
         <v>68</v>
       </c>
+      <c r="D7"/>
       <c r="E7" t="s">
         <v>69</v>
       </c>
@@ -681,37 +690,38 @@
         <v>74</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="N7" t="s">
         <v>76</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D8"/>
       <c r="E8" t="s">
         <v>79</v>
       </c>
@@ -722,44 +732,45 @@
         <v>81</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
         <v>83</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="N8" t="s">
         <v>76</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9"/>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
+      <c r="D9"/>
       <c r="E9" t="s">
         <v>86</v>
       </c>
@@ -779,10 +790,10 @@
         <v>91</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
         <v>28</v>
@@ -794,20 +805,21 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10"/>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
+      <c r="D10"/>
       <c r="E10" t="s">
         <v>94</v>
       </c>
@@ -827,13 +839,13 @@
         <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -842,20 +854,21 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11"/>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
+      <c r="D11"/>
       <c r="E11" t="s">
         <v>103</v>
       </c>
@@ -866,10 +879,10 @@
         <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
         <v>107</v>
@@ -878,7 +891,7 @@
         <v>108</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s">
         <v>28</v>
@@ -890,39 +903,40 @@
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C12"/>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
+      <c r="D12"/>
       <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="F12"/>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
       <c r="G12"/>
-      <c r="H12" t="s">
-        <v>72</v>
-      </c>
+      <c r="H12"/>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
         <v>111</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
         <v>28</v>
@@ -934,7 +948,10 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
